--- a/seating.xlsx
+++ b/seating.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10717"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -19,12 +19,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Seating!$A$1:$F$985</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4967" uniqueCount="3156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4971" uniqueCount="3156">
   <si>
     <t>FEHD Licence</t>
   </si>
@@ -9896,14 +9909,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F985"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="1" max="1" width="13.98828125" customWidth="1"/>
+    <col min="2" max="2" width="34.03125" customWidth="1"/>
+    <col min="3" max="3" width="25.9609375" customWidth="1"/>
+    <col min="4" max="4" width="13.98828125" customWidth="1"/>
+    <col min="5" max="5" width="52.05859375" customWidth="1"/>
+    <col min="6" max="6" width="11.97265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -13418,7 +13431,9 @@
       <c r="E195" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="F195" s="4"/>
+      <c r="F195" s="4" t="s">
+        <v>735</v>
+      </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
@@ -13978,9 +13993,7 @@
       <c r="E226" s="3" t="s">
         <v>738</v>
       </c>
-      <c r="F226" s="4" t="s">
-        <v>735</v>
-      </c>
+      <c r="F226" s="4"/>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A227" s="2" t="s">
@@ -17880,9 +17893,7 @@
       <c r="E442" s="3" t="s">
         <v>1443</v>
       </c>
-      <c r="F442" s="4" t="s">
-        <v>735</v>
-      </c>
+      <c r="F442" s="4"/>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A443" s="2" t="s">
@@ -18592,7 +18603,9 @@
       <c r="E481" s="3" t="s">
         <v>1569</v>
       </c>
-      <c r="F481" s="4"/>
+      <c r="F481" s="4" t="s">
+        <v>735</v>
+      </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A482" s="2" t="s">
@@ -18666,7 +18679,9 @@
       <c r="E485" s="3" t="s">
         <v>1581</v>
       </c>
-      <c r="F485" s="4"/>
+      <c r="F485" s="4" t="s">
+        <v>735</v>
+      </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A486" s="2" t="s">
@@ -18702,7 +18717,9 @@
       <c r="E487" s="3" t="s">
         <v>1586</v>
       </c>
-      <c r="F487" s="4"/>
+      <c r="F487" s="4" t="s">
+        <v>735</v>
+      </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A488" s="2" t="s">
@@ -18774,7 +18791,9 @@
       <c r="E491" s="3" t="s">
         <v>1600</v>
       </c>
-      <c r="F491" s="4"/>
+      <c r="F491" s="4" t="s">
+        <v>735</v>
+      </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A492" s="2" t="s">
@@ -26916,7 +26935,9 @@
       <c r="E942" s="3" t="s">
         <v>3008</v>
       </c>
-      <c r="F942" s="4"/>
+      <c r="F942" s="4" t="s">
+        <v>735</v>
+      </c>
     </row>
     <row r="943" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A943" s="2" t="s">
@@ -27706,9 +27727,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="100" customWidth="1"/>
+    <col min="1" max="1" width="99.94921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">

--- a/seating.xlsx
+++ b/seating.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4971" uniqueCount="3156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4977" uniqueCount="3157">
   <si>
     <t>FEHD Licence</t>
   </si>
@@ -9505,6 +9505,9 @@
   </si>
   <si>
     <t>Rows already filled in (e.g. K11 Musea, New Town Plaza) show the expected format.</t>
+  </si>
+  <si>
+    <t>Indoor</t>
   </si>
 </sst>
 </file>
@@ -14193,7 +14196,9 @@
       <c r="E237" s="3" t="s">
         <v>779</v>
       </c>
-      <c r="F237" s="4"/>
+      <c r="F237" s="4" t="s">
+        <v>735</v>
+      </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
@@ -18473,7 +18478,9 @@
       <c r="E474" s="3" t="s">
         <v>1548</v>
       </c>
-      <c r="F474" s="4"/>
+      <c r="F474" s="4" t="s">
+        <v>3156</v>
+      </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A475" s="2" t="s">
@@ -18585,7 +18592,9 @@
       <c r="E480" s="3" t="s">
         <v>1565</v>
       </c>
-      <c r="F480" s="4"/>
+      <c r="F480" s="4" t="s">
+        <v>3156</v>
+      </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A481" s="2" t="s">
@@ -18755,7 +18764,9 @@
       <c r="E489" s="3" t="s">
         <v>1594</v>
       </c>
-      <c r="F489" s="4"/>
+      <c r="F489" s="4" t="s">
+        <v>735</v>
+      </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A490" s="2" t="s">
@@ -22471,7 +22482,9 @@
       <c r="E695" s="3" t="s">
         <v>2239</v>
       </c>
-      <c r="F695" s="4"/>
+      <c r="F695" s="4" t="s">
+        <v>735</v>
+      </c>
     </row>
     <row r="696" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A696" s="2" t="s">
@@ -24707,7 +24720,9 @@
       <c r="E819" s="3" t="s">
         <v>2622</v>
       </c>
-      <c r="F819" s="4"/>
+      <c r="F819" s="4" t="s">
+        <v>735</v>
+      </c>
     </row>
     <row r="820" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A820" s="2" t="s">

--- a/seating.xlsx
+++ b/seating.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10717"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martintan/Documents/GitHub/paws-plates-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6383BE81-8DBB-4241-8832-84CC823BF7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADF2968-F293-0A42-96EE-2AF0E54FB32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19060" yWindow="1200" windowWidth="25680" windowHeight="22920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,25 +19,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Seating!$A$1:$F$985</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4977" uniqueCount="3157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5077" uniqueCount="3156">
   <si>
     <t>FEHD Licence</t>
   </si>
@@ -180,6 +167,9 @@
     <t>G/F, 1J SANDS STREET, KENNEDY TOWN, HONG KONG</t>
   </si>
   <si>
+    <t>indoor</t>
+  </si>
+  <si>
     <t>3118810675</t>
   </si>
   <si>
@@ -2244,9 +2234,6 @@
     <t>SHOP NOS. 301 &amp; 302, 3/F, AIRSIDE, 2 CONCORDE ROAD, KAI TAK, KOWLOON</t>
   </si>
   <si>
-    <t>indoor</t>
-  </si>
-  <si>
     <t>2252810525</t>
   </si>
   <si>
@@ -9505,9 +9492,6 @@
   </si>
   <si>
     <t>Rows already filled in (e.g. K11 Musea, New Town Plaza) show the expected format.</t>
-  </si>
-  <si>
-    <t>Indoor</t>
   </si>
 </sst>
 </file>
@@ -9596,7 +9580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -9609,6 +9593,7 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9912,14 +9897,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F985"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.98828125" customWidth="1"/>
-    <col min="2" max="2" width="34.03125" customWidth="1"/>
-    <col min="3" max="3" width="25.9609375" customWidth="1"/>
-    <col min="4" max="4" width="13.98828125" customWidth="1"/>
-    <col min="5" max="5" width="52.05859375" customWidth="1"/>
-    <col min="6" max="6" width="11.97265625" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="52" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -10174,1723 +10159,1747 @@
       <c r="E14" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="4"/>
+      <c r="F14" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F15" s="4"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F16" s="4"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F17" s="4"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F18" s="4"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F20" s="4"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F21" s="4"/>
+        <v>70</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F24" s="4"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F27" s="4"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F28" s="4"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F29" s="4"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F31" s="4"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F32" s="4"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F34" s="4"/>
+        <v>104</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F35" s="4"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F36" s="4"/>
+        <v>111</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F37" s="4"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F38" s="4"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F39" s="4"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F40" s="4"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F41" s="4"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F42" s="4"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F43" s="4"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F44" s="4"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F45" s="4"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F46" s="4"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F47" s="4"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F48" s="4"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F50" s="4"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F51" s="4"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F52" s="4"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F53" s="4"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F54" s="4"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F55" s="4"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F56" s="4"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F57" s="4"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F58" s="4"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F59" s="4"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F60" s="4"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F61" s="4"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F62" s="4"/>
+        <v>196</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F63" s="4"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F64" s="4"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F65" s="4"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F66" s="4"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="F67" s="4"/>
+        <v>214</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="F68" s="4"/>
+        <v>216</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F69" s="4"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F70" s="4"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F71" s="4"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F72" s="4"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F73" s="4"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F74" s="4"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F75" s="4"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F76" s="4"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F77" s="4"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F78" s="4"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F79" s="4"/>
+        <v>252</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F80" s="4"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="F81" s="4"/>
+        <v>258</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F82" s="4"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F83" s="4"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F84" s="4"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F85" s="4"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F86" s="4"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F87" s="4"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F88" s="4"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F89" s="4"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F90" s="4"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F91" s="4"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F92" s="4"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F93" s="4"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F94" s="4"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F95" s="4"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F96" s="4"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="F97" s="4"/>
+        <v>310</v>
+      </c>
+      <c r="F97" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F98" s="4"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="F99" s="4"/>
+        <v>317</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F100" s="4"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F101" s="4"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F102" s="4"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="F103" s="4"/>
+        <v>329</v>
+      </c>
+      <c r="F103" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F104" s="4"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F105" s="4"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F106" s="4"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F107" s="4"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F108" s="4"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F109" s="4"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>23</v>
@@ -11899,16 +11908,16 @@
         <v>24</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F110" s="4"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>23</v>
@@ -11917,16 +11926,16 @@
         <v>24</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F111" s="4"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>23</v>
@@ -11935,1548 +11944,1560 @@
         <v>24</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F112" s="4"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F113" s="4"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F114" s="4"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F115" s="4"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F116" s="4"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F117" s="4"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F118" s="4"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F119" s="4"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F120" s="4"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F121" s="4"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F122" s="4"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F123" s="4"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F124" s="4"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="F125" s="4"/>
+        <v>398</v>
+      </c>
+      <c r="F125" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="F126" s="4"/>
+        <v>402</v>
+      </c>
+      <c r="F126" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F127" s="4"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F128" s="4"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F129" s="4"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F130" s="4"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F131" s="4"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F132" s="4"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F133" s="4"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F134" s="4"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="F135" s="4"/>
+        <v>431</v>
+      </c>
+      <c r="F135" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="F136" s="4"/>
+        <v>435</v>
+      </c>
+      <c r="F136" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F137" s="4"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F138" s="4"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F139" s="4"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F140" s="4"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F141" s="4"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F142" s="4"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="F143" s="4"/>
+        <v>460</v>
+      </c>
+      <c r="F143" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F144" s="4"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F145" s="4"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F146" s="4"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F147" s="4"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F148" s="4"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F149" s="4"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F150" s="4"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F151" s="4"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F152" s="4"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F153" s="4"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F154" s="4"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F155" s="4"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F156" s="4"/>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F157" s="4"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F158" s="4"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F159" s="4"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F160" s="4"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F161" s="4"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F162" s="4"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F163" s="4"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F164" s="4"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F165" s="4"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F166" s="4"/>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F167" s="4"/>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F168" s="4"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F169" s="4"/>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F170" s="4"/>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A171" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F171" s="4"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F172" s="4"/>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="F173" s="4"/>
+        <v>565</v>
+      </c>
+      <c r="F173" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F174" s="4"/>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F175" s="4"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F176" s="4"/>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F177" s="4"/>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F178" s="4"/>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F179" s="4"/>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F180" s="4"/>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F181" s="4"/>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F182" s="4"/>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A183" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F183" s="4"/>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F184" s="4"/>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F185" s="4"/>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F186" s="4"/>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F187" s="4"/>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F188" s="4"/>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A189" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F189" s="4"/>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F190" s="4"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A191" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F191" s="4"/>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F192" s="4"/>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A193" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F193" s="4"/>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F194" s="4"/>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F196" s="4"/>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F197" s="4"/>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>23</v>
@@ -13485,499 +13506,509 @@
         <v>24</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F198" s="4"/>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F199" s="4"/>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F200" s="4"/>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F201" s="4"/>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="F202" s="4"/>
+        <v>663</v>
+      </c>
+      <c r="F202" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C203" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="F203" s="4"/>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C204" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F204" s="4"/>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A205" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F205" s="4"/>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>673</v>
-      </c>
-      <c r="F206" s="4"/>
+        <v>674</v>
+      </c>
+      <c r="F206" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F207" s="4"/>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="F208" s="4"/>
+        <v>679</v>
+      </c>
+      <c r="F208" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A209" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F209" s="4"/>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F210" s="4"/>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F211" s="4"/>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>691</v>
-      </c>
-      <c r="F212" s="4"/>
+        <v>692</v>
+      </c>
+      <c r="F212" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A213" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F213" s="4"/>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F214" s="4"/>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="F215" s="4"/>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F216" s="4"/>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="F217" s="4"/>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F218" s="4"/>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F219" s="4"/>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="F220" s="4"/>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A221" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="F221" s="4"/>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="F222" s="4"/>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A223" s="2" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="F223" s="4"/>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="F224" s="4"/>
+        <v>731</v>
+      </c>
+      <c r="F224" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.2">
@@ -13991,7 +14022,7 @@
         <v>737</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E226" s="3" t="s">
         <v>738</v>
@@ -14009,7 +14040,7 @@
         <v>741</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E227" s="3" t="s">
         <v>742</v>
@@ -14027,7 +14058,7 @@
         <v>745</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E228" s="3" t="s">
         <v>746</v>
@@ -14045,13 +14076,13 @@
         <v>749</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E229" s="3" t="s">
         <v>750</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.2">
@@ -14065,7 +14096,7 @@
         <v>753</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E230" s="3" t="s">
         <v>754</v>
@@ -14083,7 +14114,7 @@
         <v>757</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E231" s="3" t="s">
         <v>758</v>
@@ -14101,7 +14132,7 @@
         <v>760</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E232" s="3" t="s">
         <v>761</v>
@@ -14119,7 +14150,7 @@
         <v>764</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E233" s="3" t="s">
         <v>765</v>
@@ -14137,7 +14168,7 @@
         <v>768</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E234" s="3" t="s">
         <v>769</v>
@@ -14155,7 +14186,7 @@
         <v>771</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E235" s="3" t="s">
         <v>772</v>
@@ -14173,12 +14204,14 @@
         <v>774</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E236" s="3" t="s">
         <v>775</v>
       </c>
-      <c r="F236" s="4"/>
+      <c r="F236" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
@@ -14191,13 +14224,13 @@
         <v>778</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E237" s="3" t="s">
         <v>779</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.2">
@@ -14205,13 +14238,13 @@
         <v>780</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E238" s="3" t="s">
         <v>781</v>
@@ -14229,7 +14262,7 @@
         <v>784</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E239" s="3" t="s">
         <v>785</v>
@@ -14247,7 +14280,7 @@
         <v>788</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E240" s="3" t="s">
         <v>789</v>
@@ -14265,7 +14298,7 @@
         <v>791</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>792</v>
@@ -14283,7 +14316,7 @@
         <v>794</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E242" s="3" t="s">
         <v>795</v>
@@ -14301,7 +14334,7 @@
         <v>797</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E243" s="3" t="s">
         <v>798</v>
@@ -14319,7 +14352,7 @@
         <v>801</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E244" s="3" t="s">
         <v>802</v>
@@ -14337,12 +14370,14 @@
         <v>804</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E245" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="F245" s="4"/>
+      <c r="F245" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A246" s="2" t="s">
@@ -14355,7 +14390,7 @@
         <v>808</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E246" s="3" t="s">
         <v>809</v>
@@ -14373,7 +14408,7 @@
         <v>811</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E247" s="3" t="s">
         <v>812</v>
@@ -14391,7 +14426,7 @@
         <v>814</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E248" s="3" t="s">
         <v>815</v>
@@ -14409,7 +14444,7 @@
         <v>817</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E249" s="3" t="s">
         <v>818</v>
@@ -14427,7 +14462,7 @@
         <v>820</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E250" s="3" t="s">
         <v>821</v>
@@ -14445,7 +14480,7 @@
         <v>823</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E251" s="3" t="s">
         <v>824</v>
@@ -14463,7 +14498,7 @@
         <v>826</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E252" s="3" t="s">
         <v>827</v>
@@ -14481,7 +14516,7 @@
         <v>829</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E253" s="3" t="s">
         <v>830</v>
@@ -14499,7 +14534,7 @@
         <v>832</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E254" s="3" t="s">
         <v>833</v>
@@ -14522,7 +14557,9 @@
       <c r="E255" s="3" t="s">
         <v>837</v>
       </c>
-      <c r="F255" s="4"/>
+      <c r="F255" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A256" s="2" t="s">
@@ -14640,7 +14677,7 @@
         <v>862</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D262" s="3" t="s">
         <v>836</v>
@@ -14745,10 +14782,10 @@
         <v>882</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D268" s="3" t="s">
         <v>836</v>
@@ -15033,10 +15070,10 @@
         <v>931</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D284" s="3" t="s">
         <v>892</v>
@@ -15062,7 +15099,9 @@
       <c r="E285" s="3" t="s">
         <v>935</v>
       </c>
-      <c r="F285" s="4"/>
+      <c r="F285" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A286" s="2" t="s">
@@ -15134,7 +15173,9 @@
       <c r="E289" s="3" t="s">
         <v>948</v>
       </c>
-      <c r="F289" s="4"/>
+      <c r="F289" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A290" s="2" t="s">
@@ -15170,7 +15211,9 @@
       <c r="E291" s="3" t="s">
         <v>954</v>
       </c>
-      <c r="F291" s="4"/>
+      <c r="F291" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A292" s="2" t="s">
@@ -15206,17 +15249,19 @@
       <c r="E293" s="3" t="s">
         <v>961</v>
       </c>
-      <c r="F293" s="4"/>
+      <c r="F293" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A294" s="2" t="s">
         <v>962</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D294" s="3" t="s">
         <v>892</v>
@@ -15278,7 +15323,9 @@
       <c r="E297" s="3" t="s">
         <v>974</v>
       </c>
-      <c r="F297" s="4"/>
+      <c r="F297" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A298" s="2" t="s">
@@ -15386,7 +15433,9 @@
       <c r="E303" s="3" t="s">
         <v>993</v>
       </c>
-      <c r="F303" s="4"/>
+      <c r="F303" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A304" s="2" t="s">
@@ -15414,7 +15463,7 @@
         <v>998</v>
       </c>
       <c r="C305" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D305" s="3" t="s">
         <v>970</v>
@@ -15422,7 +15471,9 @@
       <c r="E305" s="3" t="s">
         <v>999</v>
       </c>
-      <c r="F305" s="4"/>
+      <c r="F305" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A306" s="2" t="s">
@@ -15440,7 +15491,9 @@
       <c r="E306" s="3" t="s">
         <v>1002</v>
       </c>
-      <c r="F306" s="4"/>
+      <c r="F306" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A307" s="2" t="s">
@@ -15465,10 +15518,10 @@
         <v>1006</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D308" s="3" t="s">
         <v>970</v>
@@ -15494,7 +15547,9 @@
       <c r="E309" s="3" t="s">
         <v>1011</v>
       </c>
-      <c r="F309" s="4"/>
+      <c r="F309" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A310" s="2" t="s">
@@ -15602,7 +15657,9 @@
       <c r="E315" s="3" t="s">
         <v>1032</v>
       </c>
-      <c r="F315" s="4"/>
+      <c r="F315" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A316" s="2" t="s">
@@ -15720,7 +15777,7 @@
         <v>1054</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D322" s="3" t="s">
         <v>970</v>
@@ -15756,7 +15813,7 @@
         <v>1060</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D324" s="3" t="s">
         <v>970</v>
@@ -15818,7 +15875,9 @@
       <c r="E327" s="3" t="s">
         <v>1073</v>
       </c>
-      <c r="F327" s="4"/>
+      <c r="F327" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A328" s="2" t="s">
@@ -15854,7 +15913,9 @@
       <c r="E329" s="3" t="s">
         <v>1079</v>
       </c>
-      <c r="F329" s="4"/>
+      <c r="F329" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A330" s="2" t="s">
@@ -15926,7 +15987,9 @@
       <c r="E333" s="3" t="s">
         <v>1093</v>
       </c>
-      <c r="F333" s="4"/>
+      <c r="F333" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A334" s="2" t="s">
@@ -15944,7 +16007,9 @@
       <c r="E334" s="3" t="s">
         <v>1097</v>
       </c>
-      <c r="F334" s="4"/>
+      <c r="F334" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A335" s="2" t="s">
@@ -15954,7 +16019,7 @@
         <v>862</v>
       </c>
       <c r="C335" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D335" s="3" t="s">
         <v>970</v>
@@ -16016,7 +16081,9 @@
       <c r="E338" s="3" t="s">
         <v>1109</v>
       </c>
-      <c r="F338" s="4"/>
+      <c r="F338" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A339" s="2" t="s">
@@ -16041,10 +16108,10 @@
         <v>1113</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D340" s="3" t="s">
         <v>970</v>
@@ -16059,10 +16126,10 @@
         <v>1115</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D341" s="3" t="s">
         <v>970</v>
@@ -16124,7 +16191,9 @@
       <c r="E344" s="3" t="s">
         <v>1126</v>
       </c>
-      <c r="F344" s="4"/>
+      <c r="F344" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A345" s="2" t="s">
@@ -16232,7 +16301,9 @@
       <c r="E350" s="3" t="s">
         <v>1145</v>
       </c>
-      <c r="F350" s="4"/>
+      <c r="F350" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A351" s="2" t="s">
@@ -16286,7 +16357,9 @@
       <c r="E353" s="3" t="s">
         <v>1155</v>
       </c>
-      <c r="F353" s="4"/>
+      <c r="F353" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A354" s="2" t="s">
@@ -16527,10 +16600,10 @@
         <v>1198</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C367" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D367" s="3" t="s">
         <v>1192</v>
@@ -16538,7 +16611,9 @@
       <c r="E367" s="3" t="s">
         <v>1199</v>
       </c>
-      <c r="F367" s="4"/>
+      <c r="F367" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A368" s="2" t="s">
@@ -16683,7 +16758,7 @@
         <v>1227</v>
       </c>
       <c r="F375" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.2">
@@ -16757,7 +16832,7 @@
         <v>1239</v>
       </c>
       <c r="F379" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.2">
@@ -16830,14 +16905,16 @@
       <c r="E383" s="3" t="s">
         <v>1252</v>
       </c>
-      <c r="F383" s="4"/>
+      <c r="F383" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A384" s="2" t="s">
         <v>1253</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C384" s="3" t="s">
         <v>1254</v>
@@ -16957,7 +17034,7 @@
         <v>1273</v>
       </c>
       <c r="F390" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.2">
@@ -17175,7 +17252,7 @@
         <v>1312</v>
       </c>
       <c r="F402" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.2">
@@ -17417,10 +17494,10 @@
         <v>1356</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C416" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D416" s="3" t="s">
         <v>1222</v>
@@ -17465,7 +17542,7 @@
         <v>1364</v>
       </c>
       <c r="F418" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.2">
@@ -17473,10 +17550,10 @@
         <v>1365</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C419" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D419" s="3" t="s">
         <v>1222</v>
@@ -17923,7 +18000,7 @@
         <v>1448</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C444" s="3" t="s">
         <v>24</v>
@@ -17952,7 +18029,9 @@
       <c r="E445" s="3" t="s">
         <v>1452</v>
       </c>
-      <c r="F445" s="4"/>
+      <c r="F445" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A446" s="2" t="s">
@@ -18007,7 +18086,7 @@
         <v>1462</v>
       </c>
       <c r="F448" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.2">
@@ -18051,10 +18130,10 @@
         <v>1469</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C451" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D451" s="3" t="s">
         <v>1436</v>
@@ -18069,10 +18148,10 @@
         <v>1471</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C452" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D452" s="3" t="s">
         <v>1436</v>
@@ -18080,7 +18159,9 @@
       <c r="E452" s="3" t="s">
         <v>1472</v>
       </c>
-      <c r="F452" s="4"/>
+      <c r="F452" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A453" s="2" t="s">
@@ -18153,7 +18234,7 @@
         <v>1487</v>
       </c>
       <c r="F456" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.2">
@@ -18190,7 +18271,9 @@
       <c r="E458" s="3" t="s">
         <v>1493</v>
       </c>
-      <c r="F458" s="4"/>
+      <c r="F458" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A459" s="2" t="s">
@@ -18370,7 +18453,9 @@
       <c r="E468" s="3" t="s">
         <v>1527</v>
       </c>
-      <c r="F468" s="4"/>
+      <c r="F468" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A469" s="2" t="s">
@@ -18479,7 +18564,7 @@
         <v>1548</v>
       </c>
       <c r="F474" s="4" t="s">
-        <v>3156</v>
+        <v>47</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.2">
@@ -18523,10 +18608,10 @@
         <v>1556</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C477" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D477" s="3" t="s">
         <v>1436</v>
@@ -18553,7 +18638,7 @@
         <v>1559</v>
       </c>
       <c r="F478" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.2">
@@ -18573,7 +18658,7 @@
         <v>1561</v>
       </c>
       <c r="F479" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.2">
@@ -18593,7 +18678,7 @@
         <v>1565</v>
       </c>
       <c r="F480" s="4" t="s">
-        <v>3156</v>
+        <v>47</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.2">
@@ -18613,7 +18698,7 @@
         <v>1569</v>
       </c>
       <c r="F481" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.2">
@@ -18651,7 +18736,7 @@
         <v>1574</v>
       </c>
       <c r="F483" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.2">
@@ -18689,7 +18774,7 @@
         <v>1581</v>
       </c>
       <c r="F485" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.2">
@@ -18727,7 +18812,7 @@
         <v>1586</v>
       </c>
       <c r="F487" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.2">
@@ -18765,7 +18850,7 @@
         <v>1594</v>
       </c>
       <c r="F489" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.2">
@@ -18784,7 +18869,9 @@
       <c r="E490" s="3" t="s">
         <v>1597</v>
       </c>
-      <c r="F490" s="4"/>
+      <c r="F490" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A491" s="2" t="s">
@@ -18803,7 +18890,7 @@
         <v>1600</v>
       </c>
       <c r="F491" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.2">
@@ -18877,7 +18964,7 @@
         <v>1612</v>
       </c>
       <c r="F495" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.2">
@@ -18951,7 +19038,7 @@
         <v>1623</v>
       </c>
       <c r="F499" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.2">
@@ -19078,7 +19165,9 @@
       <c r="E506" s="3" t="s">
         <v>1648</v>
       </c>
-      <c r="F506" s="4"/>
+      <c r="F506" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A507" s="2" t="s">
@@ -19096,7 +19185,9 @@
       <c r="E507" s="3" t="s">
         <v>1652</v>
       </c>
-      <c r="F507" s="4"/>
+      <c r="F507" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A508" s="2" t="s">
@@ -19157,10 +19248,10 @@
         <v>1663</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C511" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D511" s="3" t="s">
         <v>1633</v>
@@ -19168,7 +19259,9 @@
       <c r="E511" s="3" t="s">
         <v>1664</v>
       </c>
-      <c r="F511" s="4"/>
+      <c r="F511" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A512" s="2" t="s">
@@ -19438,7 +19531,9 @@
       <c r="E526" s="3" t="s">
         <v>1717</v>
       </c>
-      <c r="F526" s="4"/>
+      <c r="F526" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A527" s="2" t="s">
@@ -19474,17 +19569,19 @@
       <c r="E528" s="3" t="s">
         <v>1724</v>
       </c>
-      <c r="F528" s="4"/>
+      <c r="F528" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A529" s="2" t="s">
         <v>1725</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C529" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D529" s="3" t="s">
         <v>1633</v>
@@ -19528,7 +19625,9 @@
       <c r="E531" s="3" t="s">
         <v>1733</v>
       </c>
-      <c r="F531" s="4"/>
+      <c r="F531" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A532" s="2" t="s">
@@ -20212,7 +20311,9 @@
       <c r="E569" s="3" t="s">
         <v>1854</v>
       </c>
-      <c r="F569" s="4"/>
+      <c r="F569" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A570" s="2" t="s">
@@ -20231,7 +20332,7 @@
         <v>1857</v>
       </c>
       <c r="F570" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.2">
@@ -20239,10 +20340,10 @@
         <v>1858</v>
       </c>
       <c r="B571" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C571" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D571" s="3" t="s">
         <v>1796</v>
@@ -20257,10 +20358,10 @@
         <v>1860</v>
       </c>
       <c r="B572" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C572" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D572" s="3" t="s">
         <v>1796</v>
@@ -20394,7 +20495,9 @@
       <c r="E579" s="3" t="s">
         <v>1883</v>
       </c>
-      <c r="F579" s="4"/>
+      <c r="F579" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A580" s="2" t="s">
@@ -20476,7 +20579,7 @@
         <v>1897</v>
       </c>
       <c r="C584" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D584" s="3" t="s">
         <v>1879</v>
@@ -20620,7 +20723,7 @@
         <v>862</v>
       </c>
       <c r="C592" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D592" s="3" t="s">
         <v>1879</v>
@@ -20707,10 +20810,10 @@
         <v>1934</v>
       </c>
       <c r="B597" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C597" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D597" s="3" t="s">
         <v>1879</v>
@@ -20908,7 +21011,7 @@
         <v>998</v>
       </c>
       <c r="C608" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D608" s="3" t="s">
         <v>1964</v>
@@ -20916,7 +21019,9 @@
       <c r="E608" s="3" t="s">
         <v>1971</v>
       </c>
-      <c r="F608" s="4"/>
+      <c r="F608" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A609" s="2" t="s">
@@ -20970,7 +21075,9 @@
       <c r="E611" s="3" t="s">
         <v>1979</v>
       </c>
-      <c r="F611" s="4"/>
+      <c r="F611" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A612" s="2" t="s">
@@ -20998,7 +21105,7 @@
         <v>1984</v>
       </c>
       <c r="C613" s="3" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D613" s="3" t="s">
         <v>1964</v>
@@ -21052,7 +21159,7 @@
         <v>1993</v>
       </c>
       <c r="C616" s="3" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D616" s="3" t="s">
         <v>1964</v>
@@ -21168,7 +21275,9 @@
       <c r="E622" s="3" t="s">
         <v>2014</v>
       </c>
-      <c r="F622" s="4"/>
+      <c r="F622" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A623" s="2" t="s">
@@ -21402,7 +21511,9 @@
       <c r="E635" s="3" t="s">
         <v>2060</v>
       </c>
-      <c r="F635" s="4"/>
+      <c r="F635" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A636" s="2" t="s">
@@ -21499,10 +21610,10 @@
         <v>2078</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C641" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D641" s="3" t="s">
         <v>1964</v>
@@ -21553,10 +21664,10 @@
         <v>2086</v>
       </c>
       <c r="B644" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C644" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D644" s="3" t="s">
         <v>1964</v>
@@ -21618,7 +21729,9 @@
       <c r="E647" s="3" t="s">
         <v>2098</v>
       </c>
-      <c r="F647" s="4"/>
+      <c r="F647" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A648" s="2" t="s">
@@ -21636,17 +21749,19 @@
       <c r="E648" s="3" t="s">
         <v>2100</v>
       </c>
-      <c r="F648" s="4"/>
+      <c r="F648" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A649" s="2" t="s">
         <v>2101</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C649" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D649" s="3" t="s">
         <v>1964</v>
@@ -21744,7 +21859,9 @@
       <c r="E654" s="3" t="s">
         <v>2119</v>
       </c>
-      <c r="F654" s="4"/>
+      <c r="F654" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A655" s="2" t="s">
@@ -21967,7 +22084,7 @@
         <v>2157</v>
       </c>
       <c r="B667" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C667" s="3" t="s">
         <v>24</v>
@@ -21996,7 +22113,9 @@
       <c r="E668" s="3" t="s">
         <v>2160</v>
       </c>
-      <c r="F668" s="4"/>
+      <c r="F668" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A669" s="2" t="s">
@@ -22078,7 +22197,7 @@
         <v>2175</v>
       </c>
       <c r="C673" s="3" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D673" s="3" t="s">
         <v>2147</v>
@@ -22104,17 +22223,19 @@
       <c r="E674" s="3" t="s">
         <v>2179</v>
       </c>
-      <c r="F674" s="4"/>
+      <c r="F674" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A675" s="2" t="s">
         <v>2180</v>
       </c>
       <c r="B675" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C675" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D675" s="3" t="s">
         <v>2147</v>
@@ -22165,10 +22286,10 @@
         <v>2186</v>
       </c>
       <c r="B678" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C678" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D678" s="3" t="s">
         <v>2147</v>
@@ -22201,10 +22322,10 @@
         <v>2190</v>
       </c>
       <c r="B680" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C680" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D680" s="3" t="s">
         <v>2147</v>
@@ -22248,7 +22369,9 @@
       <c r="E682" s="3" t="s">
         <v>2199</v>
       </c>
-      <c r="F682" s="4"/>
+      <c r="F682" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A683" s="2" t="s">
@@ -22266,7 +22389,9 @@
       <c r="E683" s="3" t="s">
         <v>2201</v>
       </c>
-      <c r="F683" s="4"/>
+      <c r="F683" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A684" s="2" t="s">
@@ -22483,7 +22608,7 @@
         <v>2239</v>
       </c>
       <c r="F695" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="696" spans="1:6" x14ac:dyDescent="0.2">
@@ -22503,7 +22628,7 @@
         <v>2242</v>
       </c>
       <c r="F696" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="697" spans="1:6" x14ac:dyDescent="0.2">
@@ -22694,7 +22819,7 @@
         <v>2275</v>
       </c>
       <c r="C707" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D707" s="3" t="s">
         <v>2220</v>
@@ -22745,10 +22870,10 @@
         <v>2284</v>
       </c>
       <c r="B710" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C710" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D710" s="3" t="s">
         <v>2220</v>
@@ -22871,10 +22996,10 @@
         <v>2307</v>
       </c>
       <c r="B717" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C717" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D717" s="3" t="s">
         <v>2220</v>
@@ -22900,7 +23025,9 @@
       <c r="E718" s="3" t="s">
         <v>2311</v>
       </c>
-      <c r="F718" s="4"/>
+      <c r="F718" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="719" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A719" s="2" t="s">
@@ -22925,10 +23052,10 @@
         <v>2315</v>
       </c>
       <c r="B720" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C720" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D720" s="3" t="s">
         <v>2220</v>
@@ -23015,10 +23142,10 @@
         <v>2327</v>
       </c>
       <c r="B725" s="3" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C725" s="3" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D725" s="3" t="s">
         <v>2220</v>
@@ -23062,7 +23189,9 @@
       <c r="E727" s="3" t="s">
         <v>2334</v>
       </c>
-      <c r="F727" s="4"/>
+      <c r="F727" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="728" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A728" s="2" t="s">
@@ -23134,7 +23263,9 @@
       <c r="E731" s="3" t="s">
         <v>2349</v>
       </c>
-      <c r="F731" s="4"/>
+      <c r="F731" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="732" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A732" s="2" t="s">
@@ -23278,7 +23409,9 @@
       <c r="E739" s="3" t="s">
         <v>2377</v>
       </c>
-      <c r="F739" s="4"/>
+      <c r="F739" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="740" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A740" s="2" t="s">
@@ -23314,7 +23447,9 @@
       <c r="E741" s="3" t="s">
         <v>2385</v>
       </c>
-      <c r="F741" s="4"/>
+      <c r="F741" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="742" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A742" s="2" t="s">
@@ -23369,7 +23504,7 @@
         <v>2394</v>
       </c>
       <c r="F744" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="745" spans="1:6" x14ac:dyDescent="0.2">
@@ -23388,7 +23523,9 @@
       <c r="E745" s="3" t="s">
         <v>2397</v>
       </c>
-      <c r="F745" s="4"/>
+      <c r="F745" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A746" s="2" t="s">
@@ -23478,7 +23615,9 @@
       <c r="E750" s="3" t="s">
         <v>2414</v>
       </c>
-      <c r="F750" s="4"/>
+      <c r="F750" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="751" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A751" s="2" t="s">
@@ -23542,7 +23681,7 @@
         <v>862</v>
       </c>
       <c r="C754" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D754" s="3" t="s">
         <v>2220</v>
@@ -23604,7 +23743,9 @@
       <c r="E757" s="3" t="s">
         <v>2434</v>
       </c>
-      <c r="F757" s="4"/>
+      <c r="F757" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A758" s="2" t="s">
@@ -23629,10 +23770,10 @@
         <v>2438</v>
       </c>
       <c r="B759" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C759" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D759" s="3" t="s">
         <v>2220</v>
@@ -23676,7 +23817,9 @@
       <c r="E761" s="3" t="s">
         <v>2445</v>
       </c>
-      <c r="F761" s="4"/>
+      <c r="F761" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="762" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A762" s="2" t="s">
@@ -23701,10 +23844,10 @@
         <v>2449</v>
       </c>
       <c r="B763" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C763" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D763" s="3" t="s">
         <v>2220</v>
@@ -23766,7 +23909,9 @@
       <c r="E766" s="3" t="s">
         <v>2460</v>
       </c>
-      <c r="F766" s="4"/>
+      <c r="F766" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="767" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A767" s="2" t="s">
@@ -23802,7 +23947,9 @@
       <c r="E768" s="3" t="s">
         <v>2466</v>
       </c>
-      <c r="F768" s="4"/>
+      <c r="F768" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="769" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A769" s="2" t="s">
@@ -23892,7 +24039,9 @@
       <c r="E773" s="3" t="s">
         <v>2485</v>
       </c>
-      <c r="F773" s="4"/>
+      <c r="F773" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="774" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A774" s="2" t="s">
@@ -23917,10 +24066,10 @@
         <v>2490</v>
       </c>
       <c r="B775" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C775" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D775" s="3" t="s">
         <v>2220</v>
@@ -23928,17 +24077,19 @@
       <c r="E775" s="3" t="s">
         <v>2491</v>
       </c>
-      <c r="F775" s="4"/>
+      <c r="F775" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="776" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A776" s="2" t="s">
         <v>2492</v>
       </c>
       <c r="B776" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C776" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D776" s="3" t="s">
         <v>2220</v>
@@ -23953,10 +24104,10 @@
         <v>2494</v>
       </c>
       <c r="B777" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C777" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D777" s="3" t="s">
         <v>2220</v>
@@ -24018,7 +24169,9 @@
       <c r="E780" s="3" t="s">
         <v>2504</v>
       </c>
-      <c r="F780" s="4"/>
+      <c r="F780" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="781" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A781" s="2" t="s">
@@ -24090,7 +24243,9 @@
       <c r="E784" s="3" t="s">
         <v>2517</v>
       </c>
-      <c r="F784" s="4"/>
+      <c r="F784" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="785" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A785" s="2" t="s">
@@ -24144,7 +24299,9 @@
       <c r="E787" s="3" t="s">
         <v>2524</v>
       </c>
-      <c r="F787" s="4"/>
+      <c r="F787" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="788" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A788" s="2" t="s">
@@ -24288,7 +24445,9 @@
       <c r="E795" s="3" t="s">
         <v>2549</v>
       </c>
-      <c r="F795" s="4"/>
+      <c r="F795" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="796" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A796" s="2" t="s">
@@ -24306,7 +24465,9 @@
       <c r="E796" s="3" t="s">
         <v>2552</v>
       </c>
-      <c r="F796" s="4"/>
+      <c r="F796" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="797" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A797" s="2" t="s">
@@ -24532,7 +24693,7 @@
         <v>2175</v>
       </c>
       <c r="C809" s="3" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D809" s="3" t="s">
         <v>2578</v>
@@ -24721,7 +24882,7 @@
         <v>2622</v>
       </c>
       <c r="F819" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="820" spans="1:6" x14ac:dyDescent="0.2">
@@ -24783,10 +24944,10 @@
         <v>2632</v>
       </c>
       <c r="B823" s="3" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C823" s="3" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D823" s="3" t="s">
         <v>2618</v>
@@ -24849,7 +25010,7 @@
         <v>2643</v>
       </c>
       <c r="F826" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="827" spans="1:6" x14ac:dyDescent="0.2">
@@ -24878,7 +25039,7 @@
         <v>1897</v>
       </c>
       <c r="C828" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D828" s="3" t="s">
         <v>2618</v>
@@ -25030,7 +25191,9 @@
       <c r="E836" s="3" t="s">
         <v>2674</v>
       </c>
-      <c r="F836" s="4"/>
+      <c r="F836" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="837" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A837" s="2" t="s">
@@ -25073,10 +25236,10 @@
         <v>2682</v>
       </c>
       <c r="B839" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C839" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D839" s="3" t="s">
         <v>2618</v>
@@ -25139,7 +25302,7 @@
         <v>2693</v>
       </c>
       <c r="F842" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="843" spans="1:6" x14ac:dyDescent="0.2">
@@ -25176,7 +25339,9 @@
       <c r="E844" s="3" t="s">
         <v>2700</v>
       </c>
-      <c r="F844" s="4"/>
+      <c r="F844" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="845" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A845" s="2" t="s">
@@ -25195,7 +25360,7 @@
         <v>2703</v>
       </c>
       <c r="F845" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="846" spans="1:6" x14ac:dyDescent="0.2">
@@ -25233,7 +25398,7 @@
         <v>2709</v>
       </c>
       <c r="F847" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="848" spans="1:6" x14ac:dyDescent="0.2">
@@ -25379,7 +25544,7 @@
         <v>2733</v>
       </c>
       <c r="F855" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="856" spans="1:6" x14ac:dyDescent="0.2">
@@ -25435,7 +25600,7 @@
         <v>2743</v>
       </c>
       <c r="F858" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="859" spans="1:6" x14ac:dyDescent="0.2">
@@ -25443,10 +25608,10 @@
         <v>2744</v>
       </c>
       <c r="B859" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C859" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D859" s="3" t="s">
         <v>2618</v>
@@ -25616,7 +25781,9 @@
       <c r="E868" s="3" t="s">
         <v>2773</v>
       </c>
-      <c r="F868" s="4"/>
+      <c r="F868" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="869" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A869" s="2" t="s">
@@ -25724,7 +25891,9 @@
       <c r="E874" s="3" t="s">
         <v>2792</v>
       </c>
-      <c r="F874" s="4"/>
+      <c r="F874" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="875" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A875" s="2" t="s">
@@ -25832,7 +26001,9 @@
       <c r="E880" s="3" t="s">
         <v>2814</v>
       </c>
-      <c r="F880" s="4"/>
+      <c r="F880" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="881" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A881" s="2" t="s">
@@ -25887,7 +26058,7 @@
         <v>2823</v>
       </c>
       <c r="F883" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="884" spans="1:6" x14ac:dyDescent="0.2">
@@ -25913,10 +26084,10 @@
         <v>2826</v>
       </c>
       <c r="B885" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C885" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D885" s="3" t="s">
         <v>2618</v>
@@ -25924,7 +26095,9 @@
       <c r="E885" s="3" t="s">
         <v>2827</v>
       </c>
-      <c r="F885" s="4"/>
+      <c r="F885" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="886" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A886" s="2" t="s">
@@ -26410,7 +26583,9 @@
       <c r="E912" s="3" t="s">
         <v>2916</v>
       </c>
-      <c r="F912" s="4"/>
+      <c r="F912" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="913" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A913" s="2" t="s">
@@ -26435,10 +26610,10 @@
         <v>2920</v>
       </c>
       <c r="B914" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C914" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D914" s="3" t="s">
         <v>2618</v>
@@ -26518,7 +26693,9 @@
       <c r="E918" s="3" t="s">
         <v>2933</v>
       </c>
-      <c r="F918" s="4"/>
+      <c r="F918" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="919" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A919" s="2" t="s">
@@ -26626,7 +26803,9 @@
       <c r="E924" s="3" t="s">
         <v>2951</v>
       </c>
-      <c r="F924" s="4"/>
+      <c r="F924" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="925" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A925" s="2" t="s">
@@ -26687,10 +26866,10 @@
         <v>2961</v>
       </c>
       <c r="B928" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C928" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D928" s="3" t="s">
         <v>2950</v>
@@ -26698,7 +26877,9 @@
       <c r="E928" s="3" t="s">
         <v>2962</v>
       </c>
-      <c r="F928" s="4"/>
+      <c r="F928" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="929" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A929" s="2" t="s">
@@ -26816,7 +26997,7 @@
         <v>2984</v>
       </c>
       <c r="C935" s="3" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D935" s="3" t="s">
         <v>2950</v>
@@ -26951,7 +27132,7 @@
         <v>3008</v>
       </c>
       <c r="F942" s="4" t="s">
-        <v>735</v>
+        <v>47</v>
       </c>
     </row>
     <row r="943" spans="1:6" x14ac:dyDescent="0.2">
@@ -26977,10 +27158,10 @@
         <v>3011</v>
       </c>
       <c r="B944" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C944" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D944" s="3" t="s">
         <v>2950</v>
@@ -26988,7 +27169,9 @@
       <c r="E944" s="3" t="s">
         <v>3012</v>
       </c>
-      <c r="F944" s="4"/>
+      <c r="F944" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="945" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A945" s="2" t="s">
@@ -27013,10 +27196,10 @@
         <v>3017</v>
       </c>
       <c r="B946" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C946" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D946" s="3" t="s">
         <v>2950</v>
@@ -27024,7 +27207,9 @@
       <c r="E946" s="3" t="s">
         <v>3018</v>
       </c>
-      <c r="F946" s="4"/>
+      <c r="F946" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="947" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A947" s="2" t="s">
@@ -27211,10 +27396,10 @@
         <v>3054</v>
       </c>
       <c r="B957" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C957" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D957" s="3" t="s">
         <v>2950</v>
@@ -27643,10 +27828,10 @@
         <v>3127</v>
       </c>
       <c r="B981" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C981" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D981" s="8" t="s">
         <v>1222</v>
@@ -27667,7 +27852,7 @@
         <v>3130</v>
       </c>
       <c r="D982" s="8" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E982" s="8" t="s">
         <v>3131</v>
@@ -27703,7 +27888,7 @@
         <v>3137</v>
       </c>
       <c r="D984" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E984" s="8" t="s">
         <v>3138</v>
@@ -27730,7 +27915,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F985" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" errorTitle="Invalid value" error="Please choose indoor or outdoor (or clear the cell)." promptTitle="Seating" prompt="Choose indoor or outdoor, or leave blank if unknown." sqref="F2:F985" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"indoor,outdoor"</formula1>
     </dataValidation>
@@ -27742,9 +27927,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A16"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="99.94921875" customWidth="1"/>
+    <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">

--- a/seating.xlsx
+++ b/seating.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10717"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -19,12 +19,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Seating!$A$1:$F$985</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5077" uniqueCount="3156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5078" uniqueCount="3156">
   <si>
     <t>FEHD Licence</t>
   </si>
@@ -9897,14 +9910,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F985"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="1" max="1" width="13.98828125" customWidth="1"/>
+    <col min="2" max="2" width="34.03125" customWidth="1"/>
+    <col min="3" max="3" width="25.9609375" customWidth="1"/>
+    <col min="4" max="4" width="13.98828125" customWidth="1"/>
+    <col min="5" max="5" width="52.05859375" customWidth="1"/>
+    <col min="6" max="6" width="11.97265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -18345,7 +18358,9 @@
       <c r="E462" s="3" t="s">
         <v>1507</v>
       </c>
-      <c r="F462" s="4"/>
+      <c r="F462" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A463" s="2" t="s">
@@ -27927,9 +27942,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="100" customWidth="1"/>
+    <col min="1" max="1" width="99.94921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">

--- a/seating.xlsx
+++ b/seating.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5078" uniqueCount="3156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5079" uniqueCount="3156">
   <si>
     <t>FEHD Licence</t>
   </si>
@@ -18304,7 +18304,9 @@
       <c r="E459" s="3" t="s">
         <v>1497</v>
       </c>
-      <c r="F459" s="4"/>
+      <c r="F459" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A460" s="2" t="s">

--- a/seating.xlsx
+++ b/seating.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5079" uniqueCount="3156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5112" uniqueCount="3156">
   <si>
     <t>FEHD Licence</t>
   </si>
@@ -11250,7 +11250,9 @@
       <c r="E73" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="F73" s="4"/>
+      <c r="F73" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
@@ -11434,7 +11436,9 @@
       <c r="E83" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="F83" s="4"/>
+      <c r="F83" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
@@ -11762,7 +11766,9 @@
       <c r="E101" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="F101" s="4"/>
+      <c r="F101" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
@@ -12548,7 +12554,9 @@
       <c r="E144" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="F144" s="4"/>
+      <c r="F144" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
@@ -13506,7 +13514,9 @@
       <c r="E197" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="F197" s="4"/>
+      <c r="F197" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
@@ -14076,7 +14086,9 @@
       <c r="E228" s="3" t="s">
         <v>746</v>
       </c>
-      <c r="F228" s="4"/>
+      <c r="F228" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A229" s="2" t="s">
@@ -14204,7 +14216,9 @@
       <c r="E235" s="3" t="s">
         <v>772</v>
       </c>
-      <c r="F235" s="4"/>
+      <c r="F235" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
@@ -14806,7 +14820,9 @@
       <c r="E268" s="3" t="s">
         <v>883</v>
       </c>
-      <c r="F268" s="4"/>
+      <c r="F268" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A269" s="2" t="s">
@@ -15598,7 +15614,9 @@
       <c r="E311" s="3" t="s">
         <v>1019</v>
       </c>
-      <c r="F311" s="4"/>
+      <c r="F311" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A312" s="2" t="s">
@@ -15708,7 +15726,9 @@
       <c r="E317" s="3" t="s">
         <v>1038</v>
       </c>
-      <c r="F317" s="4"/>
+      <c r="F317" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A318" s="2" t="s">
@@ -16426,7 +16446,9 @@
       <c r="E356" s="3" t="s">
         <v>1166</v>
       </c>
-      <c r="F356" s="4"/>
+      <c r="F356" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A357" s="2" t="s">
@@ -17120,7 +17142,9 @@
       <c r="E394" s="3" t="s">
         <v>1284</v>
       </c>
-      <c r="F394" s="4"/>
+      <c r="F394" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A395" s="2" t="s">
@@ -17464,7 +17488,9 @@
       <c r="E413" s="3" t="s">
         <v>1349</v>
       </c>
-      <c r="F413" s="4"/>
+      <c r="F413" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A414" s="2" t="s">
@@ -17718,7 +17744,9 @@
       <c r="E427" s="3" t="s">
         <v>1397</v>
       </c>
-      <c r="F427" s="4"/>
+      <c r="F427" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A428" s="2" t="s">
@@ -17934,7 +17962,9 @@
       <c r="E439" s="3" t="s">
         <v>1433</v>
       </c>
-      <c r="F439" s="4"/>
+      <c r="F439" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A440" s="2" t="s">
@@ -19110,7 +19140,9 @@
       <c r="E502" s="3" t="s">
         <v>1634</v>
       </c>
-      <c r="F502" s="4"/>
+      <c r="F502" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A503" s="2" t="s">
@@ -19662,7 +19694,9 @@
       <c r="E532" s="3" t="s">
         <v>1737</v>
       </c>
-      <c r="F532" s="4"/>
+      <c r="F532" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A533" s="2" t="s">
@@ -21548,7 +21582,9 @@
       <c r="E636" s="3" t="s">
         <v>2064</v>
       </c>
-      <c r="F636" s="4"/>
+      <c r="F636" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A637" s="2" t="s">
@@ -21620,7 +21656,9 @@
       <c r="E640" s="3" t="s">
         <v>2077</v>
       </c>
-      <c r="F640" s="4"/>
+      <c r="F640" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A641" s="2" t="s">
@@ -21896,7 +21934,9 @@
       <c r="E655" s="3" t="s">
         <v>2122</v>
       </c>
-      <c r="F655" s="4"/>
+      <c r="F655" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A656" s="2" t="s">
@@ -22332,7 +22372,9 @@
       <c r="E679" s="3" t="s">
         <v>2189</v>
       </c>
-      <c r="F679" s="4"/>
+      <c r="F679" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A680" s="2" t="s">
@@ -22570,7 +22612,9 @@
       <c r="E692" s="3" t="s">
         <v>2231</v>
       </c>
-      <c r="F692" s="4"/>
+      <c r="F692" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A693" s="2" t="s">
@@ -22606,7 +22650,9 @@
       <c r="E694" s="3" t="s">
         <v>2235</v>
       </c>
-      <c r="F694" s="4"/>
+      <c r="F694" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="695" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A695" s="2" t="s">
@@ -22736,7 +22782,9 @@
       <c r="E701" s="3" t="s">
         <v>2257</v>
       </c>
-      <c r="F701" s="4"/>
+      <c r="F701" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A702" s="2" t="s">
@@ -23408,7 +23456,9 @@
       <c r="E738" s="3" t="s">
         <v>2373</v>
       </c>
-      <c r="F738" s="4"/>
+      <c r="F738" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="739" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A739" s="2" t="s">
@@ -23780,7 +23830,9 @@
       <c r="E758" s="3" t="s">
         <v>2437</v>
       </c>
-      <c r="F758" s="4"/>
+      <c r="F758" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="759" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A759" s="2" t="s">
@@ -24444,7 +24496,9 @@
       <c r="E794" s="3" t="s">
         <v>2546</v>
       </c>
-      <c r="F794" s="4"/>
+      <c r="F794" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="795" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A795" s="2" t="s">
@@ -24972,7 +25026,9 @@
       <c r="E823" s="3" t="s">
         <v>2633</v>
       </c>
-      <c r="F823" s="4"/>
+      <c r="F823" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="824" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A824" s="2" t="s">
@@ -25046,7 +25102,9 @@
       <c r="E827" s="3" t="s">
         <v>2646</v>
       </c>
-      <c r="F827" s="4"/>
+      <c r="F827" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="828" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A828" s="2" t="s">
@@ -26038,7 +26096,9 @@
       <c r="E881" s="3" t="s">
         <v>2817</v>
       </c>
-      <c r="F881" s="4"/>
+      <c r="F881" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="882" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A882" s="2" t="s">
@@ -26094,7 +26154,9 @@
       <c r="E884" s="3" t="s">
         <v>2825</v>
       </c>
-      <c r="F884" s="4"/>
+      <c r="F884" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="885" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A885" s="2" t="s">
@@ -26438,7 +26500,9 @@
       <c r="E903" s="3" t="s">
         <v>2887</v>
       </c>
-      <c r="F903" s="4"/>
+      <c r="F903" s="4" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="904" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A904" s="2" t="s">
@@ -26932,7 +26996,9 @@
       <c r="E930" s="3" t="s">
         <v>2969</v>
       </c>
-      <c r="F930" s="4"/>
+      <c r="F930" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="931" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A931" s="2" t="s">

--- a/seating.xlsx
+++ b/seating.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Seating'!$A$1:$F$980</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Seating'!$A$1:$F$981</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
@@ -72,7 +72,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -94,6 +94,11 @@
         <fgColor rgb="FFFFF3C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3C4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -107,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -128,6 +133,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F980"/>
+  <dimension ref="A1:F981"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="15"/>
   <cols>
     <col width="13.98828125" customWidth="1" min="1" max="1"/>
@@ -28644,10 +28650,38 @@
       </c>
       <c r="F980" s="4" t="n"/>
     </row>
+    <row r="981">
+      <c r="A981" s="7" t="inlineStr">
+        <is>
+          <t>3198801431</t>
+        </is>
+      </c>
+      <c r="B981" s="8" t="inlineStr">
+        <is>
+          <t>TALES</t>
+        </is>
+      </c>
+      <c r="C981" s="8" t="inlineStr">
+        <is>
+          <t>TALES</t>
+        </is>
+      </c>
+      <c r="D981" s="8" t="inlineStr">
+        <is>
+          <t>Sai Kung</t>
+        </is>
+      </c>
+      <c r="E981" s="8" t="inlineStr">
+        <is>
+          <t>G/F, 36 SEE CHEUNG STREET, SAI KUNG, NEW TERRITORIES</t>
+        </is>
+      </c>
+      <c r="F981" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F980"/>
+  <autoFilter ref="A1:F981"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F980" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please choose indoor or outdoor (or clear the cell)." promptTitle="Seating" prompt="Choose indoor or outdoor, or leave blank if unknown." type="list">
+    <dataValidation sqref="F2:F981" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please choose indoor or outdoor (or clear the cell)." promptTitle="Seating" prompt="Choose indoor or outdoor, or leave blank if unknown." type="list">
       <formula1>"indoor,outdoor"</formula1>
     </dataValidation>
   </dataValidations>

--- a/seating.xlsx
+++ b/seating.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martintan/Documents/GitHub/paws-plates-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0BFD02-B4A3-A848-9032-2CB1EF34EF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C61D21A-D3A8-F942-8AD5-EFC65A64723A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19060" yWindow="1200" windowWidth="25680" windowHeight="22920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5117" uniqueCount="3155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5118" uniqueCount="3155">
   <si>
     <t>FEHD Licence</t>
   </si>
@@ -18309,7 +18309,9 @@
       <c r="E457" s="3" t="s">
         <v>1493</v>
       </c>
-      <c r="F457" s="4"/>
+      <c r="F457" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A458" s="2" t="s">

--- a/seating.xlsx
+++ b/seating.xlsx
@@ -14387,7 +14387,9 @@
       <c r="E244" s="3" t="s">
         <v>798</v>
       </c>
-      <c r="F244" s="4"/>
+      <c r="F244" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A245" s="2" t="s">

--- a/seating.xlsx
+++ b/seating.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5118" uniqueCount="3155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5123" uniqueCount="3160">
   <si>
     <t>FEHD Licence</t>
   </si>
@@ -9490,6 +9490,21 @@
   </si>
   <si>
     <t>nothing is downloaded and nothing is changed.</t>
+  </si>
+  <si>
+    <t>2252810491</t>
+  </si>
+  <si>
+    <t>2.0 CAFE AND BAR</t>
+  </si>
+  <si>
+    <t>PORTION A OF SHOP NO. S201, 2/F, KAI TAK CRUISE TERMINAL, 33 SHING FUNG ROAD, KOWLOON</t>
+  </si>
+  <si>
+    <t>August 6</t>
+  </si>
+  <si>
+    <t>2026-08-06 19:10</t>
   </si>
 </sst>
 </file>
@@ -9912,7 +9927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F983"/>
+  <dimension ref="A1:F984"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -27971,10 +27986,28 @@
         <v>47</v>
       </c>
     </row>
+    <row r="984" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A984" s="2" t="s">
+        <v>3155</v>
+      </c>
+      <c r="B984" s="3" t="s">
+        <v>3156</v>
+      </c>
+      <c r="C984" s="3" t="s">
+        <v>3156</v>
+      </c>
+      <c r="D984" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="E984" s="3" t="s">
+        <v>3157</v>
+      </c>
+      <c r="F984" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F981" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F984" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid value" error="Please choose indoor or outdoor (or clear the cell)." promptTitle="Seating" prompt="Choose indoor or outdoor, or leave blank if unknown." sqref="F2:F981" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid value" error="Please choose indoor or outdoor (or clear the cell)." promptTitle="Seating" prompt="Choose indoor or outdoor, or leave blank if unknown." sqref="F2:F984" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"indoor,outdoor"</formula1>
     </dataValidation>
   </dataValidations>
@@ -28085,7 +28118,7 @@
         <v>3144</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>3145</v>
+        <v>3158</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -28101,7 +28134,7 @@
         <v>3148</v>
       </c>
       <c r="B3" s="13">
-        <v>979</v>
+        <v>983</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -28109,7 +28142,7 @@
         <v>3149</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>3150</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">

--- a/seating.xlsx
+++ b/seating.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19060" yWindow="1200" windowWidth="25680" windowHeight="22920" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Seating" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="READ ME" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Meta" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seating" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="READ ME" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Seating'!$A$1:$F$985</definedName>
@@ -5782,7 +5782,11 @@
           <t>SHOP NO.1404, 14/F, TOWER II, THE TWINS, 12 MUK CHUI STREET, KAI TAK, KOWLOON</t>
         </is>
       </c>
-      <c r="F185" s="4" t="n"/>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>indoor</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -7382,7 +7386,11 @@
           <t>SHOP NO. G002, G/F, AIRSIDE, 2 CONCORDE ROAD, KAI TAK, KOWLOON</t>
         </is>
       </c>
-      <c r="F240" s="4" t="n"/>
+      <c r="F240" s="4" t="inlineStr">
+        <is>
+          <t>indoor</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -7838,7 +7846,11 @@
           <t>SHOP 212A, 2/F, MARITIME SQUARE 1, 31-33 TSING KING ROAD, TSING YI, NEW TERRITORIES</t>
         </is>
       </c>
-      <c r="F256" s="4" t="n"/>
+      <c r="F256" s="4" t="inlineStr">
+        <is>
+          <t>indoor</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -8066,7 +8078,11 @@
           <t>SEATING AREA A, B AND UNIT 10, LEVEL 11, MEGABOX, ENTERPRISE SQUARE FIVE, 38 WANG CHIU ROAD, KOWLOON BAY, KOWLOON</t>
         </is>
       </c>
-      <c r="F264" s="4" t="n"/>
+      <c r="F264" s="4" t="inlineStr">
+        <is>
+          <t>indoor</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -25430,7 +25446,11 @@
           <t>2/F (PORTION), REGAL KOWLOON HOTEL, 71 MODY ROAD, TSIM SHA TSUI EAST, KOWLOON</t>
         </is>
       </c>
-      <c r="F866" s="4" t="n"/>
+      <c r="F866" s="4" t="inlineStr">
+        <is>
+          <t>indoor</t>
+        </is>
+      </c>
     </row>
     <row r="867">
       <c r="A867" s="2" t="inlineStr">
@@ -26970,7 +26990,11 @@
           <t>SHOPS NO. B141-B142, LEVEL1, YOHO MIX, 1 LONG LOK ROAD, YUEN LONG, NEW TERRITORIES</t>
         </is>
       </c>
-      <c r="F920" s="4" t="n"/>
+      <c r="F920" s="4" t="inlineStr">
+        <is>
+          <t>indoor</t>
+        </is>
+      </c>
     </row>
     <row r="921">
       <c r="A921" s="2" t="inlineStr">
@@ -27790,7 +27814,11 @@
           <t>G/F, LOTS 153 (PART) AND 154 S.A (PART) IN D.D. 102, WING PING TSUEN, SAN TIN, YUEN LONG, NEW TERRITORIES</t>
         </is>
       </c>
-      <c r="F949" s="4" t="n"/>
+      <c r="F949" s="4" t="inlineStr">
+        <is>
+          <t>indoor</t>
+        </is>
+      </c>
     </row>
     <row r="950">
       <c r="A950" s="2" t="inlineStr">

--- a/seating.xlsx
+++ b/seating.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Delisted" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Seating'!$A$1:$F$985</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Seating'!$A$1:$F$987</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F985"/>
+  <dimension ref="A1:F987"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -28852,10 +28852,66 @@
       </c>
       <c r="F985" s="16" t="inlineStr"/>
     </row>
+    <row r="986">
+      <c r="A986" s="7" t="inlineStr">
+        <is>
+          <t>2215801915</t>
+        </is>
+      </c>
+      <c r="B986" s="8" t="inlineStr">
+        <is>
+          <t>Zola Beach Bar</t>
+        </is>
+      </c>
+      <c r="C986" s="8" t="inlineStr">
+        <is>
+          <t>Zola Beach Bar</t>
+        </is>
+      </c>
+      <c r="D986" s="8" t="inlineStr">
+        <is>
+          <t>Southern</t>
+        </is>
+      </c>
+      <c r="E986" s="8" t="inlineStr">
+        <is>
+          <t>SHOP NO. 2 AND OUTSIDE SEATING ACCOMMODATION AT SHOP FRONT, G/F., NO. 90 STANLEY MAIN STREET, STANLEY, HONG KONG</t>
+        </is>
+      </c>
+      <c r="F986" s="16" t="inlineStr"/>
+    </row>
+    <row r="987">
+      <c r="A987" s="7" t="inlineStr">
+        <is>
+          <t>3161808504</t>
+        </is>
+      </c>
+      <c r="B987" s="8" t="inlineStr">
+        <is>
+          <t>HARU</t>
+        </is>
+      </c>
+      <c r="C987" s="8" t="inlineStr">
+        <is>
+          <t>旭宵食堂</t>
+        </is>
+      </c>
+      <c r="D987" s="8" t="inlineStr">
+        <is>
+          <t>Yau Tsim</t>
+        </is>
+      </c>
+      <c r="E987" s="8" t="inlineStr">
+        <is>
+          <t>AREA NO.4 AT ART PARK, WEST KOWLOON CULTURAL DISTRICT, KOWLOON</t>
+        </is>
+      </c>
+      <c r="F987" s="16" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F985"/>
+  <autoFilter ref="A1:F987"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F985" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F987" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"indoor,outdoor"</formula1>
     </dataValidation>
   </dataValidations>
@@ -29005,7 +29061,7 @@
       </c>
       <c r="B1" s="12" t="inlineStr">
         <is>
-          <t>August 10</t>
+          <t>August 11</t>
         </is>
       </c>
     </row>
@@ -29028,7 +29084,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>984</v>
+        <v>986</v>
       </c>
     </row>
     <row r="4">
@@ -29039,7 +29095,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>2026-08-10 15:29</t>
+          <t>2026-08-11 16:04</t>
         </is>
       </c>
     </row>

--- a/seating.xlsx
+++ b/seating.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Delisted" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Seating'!$A$1:$F$987</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Seating'!$A$1:$F$988</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F987"/>
+  <dimension ref="A1:F988"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -28908,10 +28908,38 @@
       </c>
       <c r="F987" s="16" t="inlineStr"/>
     </row>
+    <row r="988">
+      <c r="A988" s="7" t="inlineStr">
+        <is>
+          <t>2261824223</t>
+        </is>
+      </c>
+      <c r="B988" s="8" t="inlineStr">
+        <is>
+          <t>HTIKE EASY</t>
+        </is>
+      </c>
+      <c r="C988" s="8" t="inlineStr">
+        <is>
+          <t>泰簡</t>
+        </is>
+      </c>
+      <c r="D988" s="8" t="inlineStr">
+        <is>
+          <t>Yau Tsim</t>
+        </is>
+      </c>
+      <c r="E988" s="8" t="inlineStr">
+        <is>
+          <t>SHOP 5, G/F, PO FAT BUILDING, NOS. 273-285 TEMPLE STREET, KOWLOON</t>
+        </is>
+      </c>
+      <c r="F988" s="16" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F987"/>
+  <autoFilter ref="A1:F988"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F987" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F988" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"indoor,outdoor"</formula1>
     </dataValidation>
   </dataValidations>
@@ -29061,7 +29089,7 @@
       </c>
       <c r="B1" s="12" t="inlineStr">
         <is>
-          <t>August 11</t>
+          <t>August 12</t>
         </is>
       </c>
     </row>
@@ -29084,7 +29112,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="4">
@@ -29095,7 +29123,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>2026-08-11 16:04</t>
+          <t>2026-08-12 16:09</t>
         </is>
       </c>
     </row>

--- a/seating.xlsx
+++ b/seating.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Delisted" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Seating'!$A$1:$F$988</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Seating'!$A$1:$F$991</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F988"/>
+  <dimension ref="A1:F991"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -28960,10 +28960,94 @@
       </c>
       <c r="F988" s="20" t="inlineStr"/>
     </row>
+    <row r="989">
+      <c r="A989" s="18" t="inlineStr">
+        <is>
+          <t>3197802312</t>
+        </is>
+      </c>
+      <c r="B989" s="19" t="inlineStr">
+        <is>
+          <t>Moon Ocean</t>
+        </is>
+      </c>
+      <c r="C989" s="19" t="inlineStr">
+        <is>
+          <t>Moon Ocean</t>
+        </is>
+      </c>
+      <c r="D989" s="19" t="inlineStr">
+        <is>
+          <t>Sha Tin</t>
+        </is>
+      </c>
+      <c r="E989" s="19" t="inlineStr">
+        <is>
+          <t>SHOP A, G/F &amp; COCKLOFT, HING WAN HOUSE, 74-76 CHIK CHUEN STREET, TAI WAI, SHA TIN, NEW TERRITORIES</t>
+        </is>
+      </c>
+      <c r="F989" s="20" t="inlineStr"/>
+    </row>
+    <row r="990">
+      <c r="A990" s="18" t="inlineStr">
+        <is>
+          <t>2263809071</t>
+        </is>
+      </c>
+      <c r="B990" s="19" t="inlineStr">
+        <is>
+          <t>URBAN Cafe</t>
+        </is>
+      </c>
+      <c r="C990" s="19" t="inlineStr">
+        <is>
+          <t>URBAN Cafe</t>
+        </is>
+      </c>
+      <c r="D990" s="19" t="inlineStr">
+        <is>
+          <t>Sham Shui Po</t>
+        </is>
+      </c>
+      <c r="E990" s="19" t="inlineStr">
+        <is>
+          <t>PORTION A OF UNIT 103, 1/F, LAI SUN COMMERCIAL CENTRE, 680 CHEUNG SHA WAN ROAD, LAI CHI KOK, KOWLOON</t>
+        </is>
+      </c>
+      <c r="F990" s="20" t="inlineStr"/>
+    </row>
+    <row r="991">
+      <c r="A991" s="18" t="inlineStr">
+        <is>
+          <t>3194803299</t>
+        </is>
+      </c>
+      <c r="B991" s="19" t="inlineStr">
+        <is>
+          <t>MASAM</t>
+        </is>
+      </c>
+      <c r="C991" s="19" t="inlineStr">
+        <is>
+          <t>MASAM</t>
+        </is>
+      </c>
+      <c r="D991" s="19" t="inlineStr">
+        <is>
+          <t>Yuen Long</t>
+        </is>
+      </c>
+      <c r="E991" s="19" t="inlineStr">
+        <is>
+          <t>SHOP D, G/F, LEE FAT HOUSE, NO. 5 YAN LOK SQUARE, YUEN LONG, NEW TERRITORIES</t>
+        </is>
+      </c>
+      <c r="F991" s="20" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F988"/>
+  <autoFilter ref="A1:F991"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F988" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F991" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"indoor,outdoor"</formula1>
     </dataValidation>
   </dataValidations>
@@ -29113,7 +29197,7 @@
       </c>
       <c r="B1" s="12" t="inlineStr">
         <is>
-          <t>August 18</t>
+          <t>August 19</t>
         </is>
       </c>
     </row>
@@ -29136,7 +29220,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>987</v>
+        <v>990</v>
       </c>
     </row>
     <row r="4">
@@ -29147,7 +29231,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>2026-08-18 15:30</t>
+          <t>2026-08-19 15:30</t>
         </is>
       </c>
     </row>

--- a/seating.xlsx
+++ b/seating.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Delisted" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Seating'!$A$1:$F$991</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Seating'!$A$1:$F$992</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F991"/>
+  <dimension ref="A1:F992"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -29044,10 +29044,38 @@
       </c>
       <c r="F991" s="20" t="inlineStr"/>
     </row>
+    <row r="992">
+      <c r="A992" s="18" t="inlineStr">
+        <is>
+          <t>3118809361</t>
+        </is>
+      </c>
+      <c r="B992" s="19" t="inlineStr">
+        <is>
+          <t>For Single</t>
+        </is>
+      </c>
+      <c r="C992" s="19" t="inlineStr">
+        <is>
+          <t>For Single</t>
+        </is>
+      </c>
+      <c r="D992" s="19" t="inlineStr">
+        <is>
+          <t>Central/Western</t>
+        </is>
+      </c>
+      <c r="E992" s="19" t="inlineStr">
+        <is>
+          <t>SHOP D, G/F., FULL HARVEST BUILDING, 6-18 HAU WO STREET, HONG KONG</t>
+        </is>
+      </c>
+      <c r="F992" s="20" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F991"/>
+  <autoFilter ref="A1:F992"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F991" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F992" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"indoor,outdoor"</formula1>
     </dataValidation>
   </dataValidations>
@@ -29197,7 +29225,7 @@
       </c>
       <c r="B1" s="12" t="inlineStr">
         <is>
-          <t>August 19</t>
+          <t>August 20</t>
         </is>
       </c>
     </row>
@@ -29220,7 +29248,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="4">
@@ -29231,7 +29259,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>2026-08-19 15:30</t>
+          <t>2026-08-20 15:33</t>
         </is>
       </c>
     </row>

--- a/seating.xlsx
+++ b/seating.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martintan/Developer/paws-plates-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A5BC4D-8368-C245-A41B-0F08EF97DC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE1B6A0-7E34-ED47-8797-0ECCBF0436FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5231" uniqueCount="3215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5233" uniqueCount="3215">
   <si>
     <t>FEHD Licence</t>
   </si>
@@ -10609,7 +10609,9 @@
       <c r="E26" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F26" s="4"/>
+      <c r="F26" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
@@ -10901,7 +10903,9 @@
       <c r="E42" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F42" s="4"/>
+      <c r="F42" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">

--- a/seating.xlsx
+++ b/seating.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martintan/Developer/paws-plates-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE1B6A0-7E34-ED47-8797-0ECCBF0436FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73C36C2-7420-3841-B41A-8CC9841DB2E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5233" uniqueCount="3215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5234" uniqueCount="3215">
   <si>
     <t>FEHD Licence</t>
   </si>
@@ -18853,7 +18853,9 @@
       <c r="E473" s="3" t="s">
         <v>1540</v>
       </c>
-      <c r="F473" s="4"/>
+      <c r="F473" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A474" s="2" t="s">

--- a/seating.xlsx
+++ b/seating.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5237" uniqueCount="3215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5238" uniqueCount="3215">
   <si>
     <t>FEHD Licence</t>
   </si>
@@ -10059,7 +10059,7 @@
     <col min="2" max="2" width="34.03125" customWidth="1"/>
     <col min="3" max="3" width="25.9609375" customWidth="1"/>
     <col min="4" max="4" width="13.98828125" customWidth="1"/>
-    <col min="5" max="5" width="255.73046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.53515625" customWidth="1"/>
     <col min="6" max="6" width="11.97265625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10961,7 +10961,9 @@
       <c r="E49" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="F49" s="4"/>
+      <c r="F49" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">

--- a/seating.xlsx
+++ b/seating.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5238" uniqueCount="3215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5239" uniqueCount="3215">
   <si>
     <t>FEHD Licence</t>
   </si>
@@ -24795,7 +24795,9 @@
       <c r="E800" s="3" t="s">
         <v>2556</v>
       </c>
-      <c r="F800" s="4"/>
+      <c r="F800" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="801" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A801" s="2" t="s">
